--- a/incoming/forms_latest.xlsx
+++ b/incoming/forms_latest.xlsx
@@ -28018,7 +28018,7 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <x:tableParts count="1">
-    <x:tablePart r:id="R6662dc7eb8c74a34"/>
+    <x:tablePart r:id="R79fb252338974b4e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/incoming/forms_latest.xlsx
+++ b/incoming/forms_latest.xlsx
@@ -28018,7 +28018,7 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <x:tableParts count="1">
-    <x:tablePart r:id="R79fb252338974b4e"/>
+    <x:tablePart r:id="Rec3c16b648da49a1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/incoming/forms_latest.xlsx
+++ b/incoming/forms_latest.xlsx
@@ -28018,7 +28018,7 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <x:tableParts count="1">
-    <x:tablePart r:id="Rec3c16b648da49a1"/>
+    <x:tablePart r:id="Rdc7827943ac8442c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/incoming/forms_latest.xlsx
+++ b/incoming/forms_latest.xlsx
@@ -28018,7 +28018,7 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <x:tableParts count="1">
-    <x:tablePart r:id="Rdc7827943ac8442c"/>
+    <x:tablePart r:id="R9e6553eda5c44b48"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/incoming/forms_latest.xlsx
+++ b/incoming/forms_latest.xlsx
@@ -28018,7 +28018,7 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <x:tableParts count="1">
-    <x:tablePart r:id="R9e6553eda5c44b48"/>
+    <x:tablePart r:id="Rdc799fe820e9482b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/incoming/forms_latest.xlsx
+++ b/incoming/forms_latest.xlsx
@@ -28018,7 +28018,7 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <x:tableParts count="1">
-    <x:tablePart r:id="Rdc799fe820e9482b"/>
+    <x:tablePart r:id="Rf204e3a7406340aa"/>
   </x:tableParts>
 </x:worksheet>
 </file>